--- a/results/monthly_investor_report_2026-09-16.xlsx
+++ b/results/monthly_investor_report_2026-09-16.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +180,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,13 +191,16 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -577,13 +580,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -630,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -647,7 +650,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Piyasa Rejimi: Risk ON</t>
+          <t>Piyasa Rejimi: Risk OFF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -664,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aktif Model: volume_heavy</t>
+          <t>Aktif Model: low_volatility</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -681,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 51.86/100</t>
+          <t>Güven Puanı: 64.21/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -741,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, BIMAS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
+          <t>AL: KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -758,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>AZALT: BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -775,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>ÇIK: THYAO.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -792,7 +795,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %50</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -890,7 +893,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 5</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -947,7 +950,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 5</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -961,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.12307111833361</v>
+        <v>0.2118012179582496</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12307.111833361</v>
+        <v>21180.12179582496</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>467.5182290732529</v>
+        <v>492.8207489184861</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>214.3444492591615</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>196.175</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.759752954882472</v>
+        <v>0.3518217892616204</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -990,12 +993,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %50</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1004,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1083549289094442</v>
+        <v>0.2046838490225011</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10835.49289094442</v>
+        <v>20468.38490225011</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>526.5324195262998</v>
+        <v>677.8604291940321</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>425.2045855012605</v>
+        <v>124.9038996016319</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>385.225</v>
+        <v>114.855001449585</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9718661159684575</v>
+        <v>0.662348722120733</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1036,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1045,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09211535586320244</v>
+        <v>0.1835149330192493</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9211.535586320244</v>
+        <v>18351.49330192493</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>305.0624412184431</v>
+        <v>544.659007315847</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>124.9038996016319</v>
+        <v>89.42764341974173</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>114.855001449585</v>
+        <v>82.50749855041504</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.662348722120733</v>
+        <v>0.5935854901341648</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1072,124 +1075,42 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.08923779370436544</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>8923.779370436543</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>549.1557643887553</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>1.230769479147021</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.08722080318937789</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>8722.080318937789</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>364.3891427389418</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.5942894806665029</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K25"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1286,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1429,37 +1350,37 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>206.5</v>
+        <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.039087920591243</v>
+        <v>-0.0339316179450966</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.1206226545342643</v>
+        <v>0.0770489383118369</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>198.4283443979083</v>
+        <v>391.7407289232634</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>214.3444492591615</v>
+        <v>413.2162352085374</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>231.4085781613256</v>
+        <v>436.7433444854499</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>196.175</v>
+        <v>385.225</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1467,7 +1388,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1486,45 +1407,45 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>401.75</v>
+        <v>206.5</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.0985715365910573</v>
+        <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>-0.003584755659184</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>0.1274261934904716</v>
+        <v>0.0690438632887718</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>400.3098244139228</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>452.943473234797</v>
+        <v>220.7575577691314</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="L9" s="16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M9" s="16" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
@@ -1533,64 +1454,64 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.0954999923706054</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>0.09315584596891301</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>22.93440914802076</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N10" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0446735791747727</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>115.4989657354824</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>124.9038996016319</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>135.8966593492442</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>114.855001449585</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1600,515 +1521,230 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0855565177750571</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1267042006856777</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>408.636624115174</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>452.653412625471</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0082994402169681</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1486667759327886</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>402.1345769920194</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>425.2045855012605</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>465.7843776407458</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>385.225</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="D12" s="17" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0450302501162372</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0884521142598899</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>82.93912132023661</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>89.42764341974173</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>94.53206446262533</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>82.50749855041504</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>38.22000122070312</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0842967976871922</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1015857338863732</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>38.23563010156546</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>42.10260809384634</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0762004294665497</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.0475785896346643</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>261.0262798277541</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>285.9889549702634</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>120.9000015258789</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0371959299442395</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0.1272217020935506</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>116.4030135388639</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>124.9038996016319</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>136.2811055031141</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>114.855001449585</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N13" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="M13" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>95.75</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.06865539483568921</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0289374356535263</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>93.01664919513574</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>98.52075946382514</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="D14" s="20" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.082926169656068</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.1059737014525552</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>272.1274167124678</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>301.1013402204582</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="16" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>65.19999694824219</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.0621387669809665</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.1086638342048738</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>67.19669226720924</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>72.28487860678426</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.0702987015861401</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>0.0831932668372119</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>37.67346049834082</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>84.30000305175781</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0181378772961786</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>0.1293435773389155</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>82.77097994033755</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>95.20366701615366</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>145.1999969482422</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0392156862745097</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.1293359288901121</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>139.5058794208602</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>145.0972359231034</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>163.9795734283845</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>137.9399971008301</v>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>32.11999893188477</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0532446188809735</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.0428598924856524</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="I19" s="23" t="n">
-        <v>31.50772556218617</v>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>33.49665863274462</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M14" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2232,7 +1868,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -2242,20 +1878,20 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0043774020903055</v>
+        <v>0.0072916582962114</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0551865264188744</v>
+        <v>0.0413608561912206</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1088043175022459</v>
+        <v>0.1851961795211201</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>0.2057032864944392</v>
+        <v>-0.0623598620860903</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -2263,10 +1899,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0200019040925806</v>
+        <v>0.0188637341167536</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
     </row>
     <row r="5">
@@ -2275,84 +1911,84 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.0067339775737629</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.034051092416993</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.0985692087568079</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.2031171068964992</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0194217173689601</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0.08949152542372869</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.772165881818355</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.5754901960784313</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.09061475678536079</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0266079182148352</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>-0.003584755659184</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0.0955613556219225</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>0.044820698304274</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>0.0595959773052476</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>0.1643757802273222</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>0.0406349141733305</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0</v>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>-0.064965207483533</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>-0.1604166560702853</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0918000573807312</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.1338440657530808</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.0168100770079203</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
@@ -2361,600 +1997,600 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.07419786096256679</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.7927264125750395</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.5974155069582505</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.0866514907563507</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0264956263736686</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0679401059595536</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.0665440612239525</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.2150456013908888</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0056807080181966</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>-0.0666308906426155</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>-0.16329483698748</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.2434669323574443</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.0447946090151196</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0144115919578272</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0522764930412542</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.1775609458365091</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.1068369587850867</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.0974086401731955</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.0172418278494896</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0125688346543615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.0915141430948419</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.1689497716894977</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>-0.0737913486005089</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>-0.0009174564930963</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>0.0173415165449425</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0274615272586047</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.2138603175563069</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1928849256560219</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.0526434538225228</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.0170949295625193</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.006131117760765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0.0585267338684687</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.0274240677693482</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.031465063168498</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0.1705560918196227</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0191191082032721</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0355156641914875</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.002557432846991</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>-0.0774536319509322</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.130500030517578</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.228324143503479</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.0673904056469028</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0257858693771773</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.019070255160478</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0254237288135592</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1799698795180723</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.0768923210325955</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0341755137155445</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0228770438599459</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.0538656516832387</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1872618098419274</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.3081556953641494</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.0216399265741287</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0175418542292546</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.0006695213718759</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>-0.0748792270531401</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>-0.1745689655172413</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>-0.1358303487115206</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.2731285195859629</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0.0197620982238175</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0556585878468132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0557377049180327</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.1235544735240413</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0549450549450549</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.1018704487088503</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0299429051249194</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0485096508933775</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0362158835532249</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.1960542765109</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.1122733625312385</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>0.2410422103922216</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0.0213786434561666</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.05159344410234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.0108695180015409</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1487750574201126</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0885889870129208</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.387106135015776</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>0.0026233549743024</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.1936708862796933</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>-0.1256381990168611</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0.3991606220660881</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.031520714084673</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>0.026262986561954</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.06799392425498541</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0627906858458999</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>-0.1425531806675255</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>-0.0620008227748822</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.1044133754393505</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>-0.07860016151729959</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.2477752140987634</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>-0.1072818415636823</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0.0655210596212267</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="15" t="n">
-        <v>0.0173661554830595</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0694849506302555</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.1458519063039557</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>-0.122364790658432</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.2636171930649325</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0205145061613839</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0411765154670266</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.1641026032276642</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.0744198020732777</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.225460329022473</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0223810594655514</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0832894033155693</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>-0.1172589484177429</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.2518786862216586</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.07263925691405849</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.0267034739778493</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0517435140063752</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>-0.1553106164932827</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>-0.0892681064853825</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.1017734892899173</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>0.0180337362813238</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.0745501285347043</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.08860759493670881</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>0.1232449297971918</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>-0.1014754690653146</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0303591105771636</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0245003718359859</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0396825404834755</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1933333502875434</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.1791972755340619</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>0.0432479046991434</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.01768194495492</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>0.0206185567010308</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.173120728929385</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.0450871551413537</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.062282119385654</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0234029498955229</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.0445250258600058</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0930232558139535</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.1515151515151515</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0586206896551724</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.0162517774614465</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0176619745094825</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.1028940851473592</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.07704569731734751</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.1616795390608436</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.231415942706893</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.0099801366801068</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.014927802410026</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.1658137063821738</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0801832584158213</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.2146699820643947</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0817610248078556</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>0.062087038248501</v>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0246165692883249</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.0550632718243176</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1663875043897771</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.293087096547894</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.0036869731660258</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0190864561409881</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0283622708857007</v>
+      <c r="J20" s="27" t="n">
+        <v>0.0235895708006696</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.0248447886632294</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3012,7 +2648,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, BIMAS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
+          <t>KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -3024,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -3036,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>THYAO.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -3048,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, TOASO.IS, THYAO.IS, ARCLK.IS, FROTO.IS</t>
+          <t>SAHOL.IS, PGSUS.IS, PETKM.IS, EREGL.IS, FROTO.IS, TCELL.IS, ASELS.IS, AKBNK.IS, SISE.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -3060,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3072,7 +2708,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3143,7 +2779,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3167,7 +2803,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3179,7 +2815,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3251,7 +2887,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3275,7 +2911,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3323,7 +2959,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3357,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3381,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13509.7998046875</v>
+        <v>13284.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3391,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13489.76401855469</v>
+        <v>13501.69251953125</v>
       </c>
     </row>
     <row r="6">
@@ -3402,7 +3038,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Risk ON</t>
+          <t>Risk OFF</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3050,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>volume_heavy</t>
+          <t>low_volatility</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3436,7 +3072,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
+          <t>BIST100 MA200 altında olduğu için savunmacı rejim izleniyor.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3096,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3482,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3546,22 +3182,22 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="28" t="n">
         <v>360</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="29" t="n">
         <v>-0.09887359198998746</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="28" t="n">
         <v>-69654.44262507732</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H4" s="28" t="n">
+      <c r="G4" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3576,22 +3212,22 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="28" t="n">
         <v>206.5</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.0482233502538072</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>140153.6803430272</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H5" s="28" t="n">
+      <c r="G5" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3606,22 +3242,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="28" t="n">
         <v>84.30000305175781</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="29" t="n">
         <v>-0.1264248388418879</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>-11101.93142037037</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H6" s="28" t="n">
+      <c r="G6" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3636,89 +3272,89 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="28" t="n">
         <v>120.9000015258789</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="29" t="n">
         <v>-0.09370309552116773</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>-453776.1194554595</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H7" s="28" t="n">
+      <c r="G7" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>299.75</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-0.09174311926605505</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>-20640.73562494843</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H8" s="28" t="n">
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>34.77999877929688</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.1049923254496258</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-22854.86544006292</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-0.1049923254496258</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>-22854.86544006292</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H9" s="28" t="n">
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3726,22 +3362,22 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E10" s="28" t="n">
+      <c r="C10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H10" s="28" t="n">
+      <c r="F10" s="28" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>

--- a/results/monthly_investor_report_2026-09-16.xlsx
+++ b/results/monthly_investor_report_2026-09-16.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2118012179582496</v>
+        <v>0.2118012179582497</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21180.12179582496</v>
+        <v>21180.12179582497</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>492.8207489184861</v>
+        <v>492.8207489184928</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>211.3048583304997</v>
@@ -982,7 +982,7 @@
         <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3518217892616204</v>
+        <v>0.3518217892616246</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2046838490225011</v>
+        <v>0.204683849022501</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20468.38490225011</v>
+        <v>20468.3849022501</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>677.8604291940321</v>
+        <v>677.860429194032</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>124.9038996016319</v>
@@ -1057,7 +1057,7 @@
         <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>544.659007315847</v>
+        <v>544.6590073158468</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>89.42764341974173</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
         <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316179450966</v>
+        <v>-0.0339316179450965</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1422,7 +1422,7 @@
         <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.0690438632887718</v>
@@ -1539,7 +1539,7 @@
         <v>0.0171415659369608</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.1267042006856777</v>
+        <v>0.1267042006856775</v>
       </c>
       <c r="H11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1548,7 +1548,7 @@
         <v>408.636624115174</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>452.653412625471</v>
+        <v>452.6534126254709</v>
       </c>
       <c r="K11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0072916582962114</v>
+        <v>0.0072916582962112</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>0.0413608561912206</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-0.0067339775737629</v>
+        <v>-0.006733977573763</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.034051092416993</v>
@@ -1945,7 +1945,7 @@
         <v>0.0194217173689601</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -2014,7 +2014,7 @@
         <v>0.07419786096256679</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.7927264125750395</v>
+        <v>0.7927264125750397</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>0.5974155069582505</v>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.0666308906426155</v>
+        <v>-0.0666308906426154</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-0.16329483698748</v>
+        <v>-0.1632948369874799</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0.2434669323574443</v>
+        <v>-0.2434669323574442</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0.0447946090151196</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0144115919578272</v>
+        <v>0.0144115919578273</v>
       </c>
       <c r="K8" s="18" t="n">
         <v>0.0296792745067082</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0172418278494896</v>
+        <v>0.0172418278494895</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.0125688346543615</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0173415165449425</v>
+        <v>0.0173415165449426</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>-0.0438597808507175</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0355156641914875</v>
+        <v>0.0355156641914876</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>0.002557432846991</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0257858693771773</v>
+        <v>0.0257858693771772</v>
       </c>
       <c r="K13" s="23" t="n">
         <v>0.019070255160478</v>
@@ -2318,7 +2318,7 @@
         <v>-0.1799698795180723</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.0768923210325955</v>
+        <v>-0.0768923210325954</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>-0.0341755137155445</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0228770438599459</v>
+        <v>0.022877043859946</v>
       </c>
       <c r="K14" s="25" t="n">
         <v>-0.000450260009301</v>
@@ -2404,7 +2404,7 @@
         <v>-0.1745689655172413</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>-0.1358303487115206</v>
+        <v>-0.1358303487115205</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.2731285195859629</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0213786434561666</v>
+        <v>0.0213786434561665</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>0.05159344410234</v>
@@ -2533,7 +2533,7 @@
         <v>-0.1936708862796933</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>-0.1256381990168611</v>
+        <v>-0.1256381990168612</v>
       </c>
       <c r="H19" s="27" t="n">
         <v>0.3991606220660881</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0235895708006696</v>
+        <v>0.0235895708006695</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.0248447886632294</v>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>

--- a/results/monthly_investor_report_2026-09-16.xlsx
+++ b/results/monthly_investor_report_2026-09-16.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>
